--- a/artfynd/A 55761-2023 artfynd.xlsx
+++ b/artfynd/A 55761-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55761-2023 artfynd.xlsx
+++ b/artfynd/A 55761-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>117767984</v>
       </c>
       <c r="B45" t="n">
-        <v>94610</v>
+        <v>94612</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 55761-2023 artfynd.xlsx
+++ b/artfynd/A 55761-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112418652</v>
       </c>
       <c r="B2" t="n">
-        <v>8414</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Harsjön (Lilla Harsjön), Upl</t>
+          <t>Lilla Harsjön, Lilla Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -791,7 +791,7 @@
         <v>112418454</v>
       </c>
       <c r="B3" t="n">
-        <v>90937</v>
+        <v>91863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Harsjön (Lilla Harsjön), Upl</t>
+          <t>Lilla Harsjön, Lilla Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1124,7 +1124,7 @@
         <v>112418706</v>
       </c>
       <c r="B6" t="n">
-        <v>90937</v>
+        <v>91863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Harsjön (Lilla Harsjön), Upl</t>
+          <t>Lilla Harsjön, Lilla Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1237,7 +1237,7 @@
         <v>112417724</v>
       </c>
       <c r="B7" t="n">
-        <v>78336</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Harsjön (Lilla Harsjön), Upl</t>
+          <t>Lilla Harsjön, Lilla Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -5238,7 +5238,7 @@
         <v>113400585</v>
       </c>
       <c r="B42" t="n">
-        <v>5165</v>
+        <v>5169</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilla Harsjön (Lilla Harsjön), Upl</t>
+          <t>Lilla Harsjön, Lilla Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">

--- a/artfynd/A 55761-2023 artfynd.xlsx
+++ b/artfynd/A 55761-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>112418454</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>112418706</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>112417724</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
